--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/sk-sk.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/sk-sk.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DD0E8D-7BEC-4EB3-9FC9-C3DEF71FD4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{63DD0E8D-7BEC-4EB3-9FC9-C3DEF71FD4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{545E71E4-4D59-4698-9847-53591A906D3D}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6640,17 +6640,13 @@
       <c r="K7" s="43"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" s="15" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-    </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="8"/>
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
         <v>2</v>
@@ -6659,7 +6655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" s="8" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
         <v>0</v>
@@ -6667,14 +6663,8 @@
       <c r="D10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:12" s="8" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="22"/>
       <c r="C11" s="21" t="s">
         <v>1</v>
@@ -6682,12 +6672,6 @@
       <c r="D11" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C12" s="1"/>
@@ -6940,7 +6924,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <dataConsolidate/>
-  <conditionalFormatting sqref="F8:I1048576 F1:I1 H2:J5">
+  <conditionalFormatting sqref="F12:I1048576 F1:I1 H2:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -6959,7 +6943,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:I8 H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
